--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-easy.xlsx
@@ -466,10 +466,10 @@
         <v>Khả năng tự động phát hiện mọi lỗi logic nghiệp vụ mà không cần con người viết kịch bản test trước — tự phát hiện lỗi không cần kịch bản</v>
       </c>
       <c r="H2" t="str">
+        <v>Hoàn toàn loại bỏ nhu cầu tuyển dụng nhân sự QA trong suốt toàn bộ dự án phần mềm — loại bỏ nhân sự QA</v>
+      </c>
+      <c r="I2" t="str">
         <v>Khả năng tự viết lại mã nguồn code sửa lỗi cho lập trình viên khi phát hiện ra bug — tự sửa code hệ thống</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Hoàn toàn loại bỏ nhu cầu tuyển dụng nhân sự QA trong suốt toàn bộ dự án phần mềm — loại bỏ nhân sự QA</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -495,10 +495,10 @@
         <v>ID — thuộc tính định danh duy nhất của phần tử HTML trên trang — locator ID duy nhất</v>
       </c>
       <c r="G3" t="str">
+        <v>TagName — tên của thẻ HTML (như &lt;div&gt;, &lt;p&gt;) — locator tên thẻ HTML</v>
+      </c>
+      <c r="H3" t="str">
         <v>XPath — đường dẫn tuyệt đối đi từ thẻ gốc HTML xuống dưới — locator đường dẫn tuyệt đối</v>
-      </c>
-      <c r="H3" t="str">
-        <v>TagName — tên của thẻ HTML (như &lt;div&gt;, &lt;p&gt;) — locator tên thẻ HTML</v>
       </c>
       <c r="I3" t="str">
         <v>LinkText — đoạn chuỗi văn bản hiển thị của thẻ liên kết — locator văn bản liên kết</v>
@@ -524,19 +524,19 @@
         <v>POM là design pattern phổ biến nhất trong Automation. Mỗi trang web (Page) được đại diện bởi một class. Khi giao diện thay đổi (ví dụ đổi ID của nút bấm), ta chỉ cần sửa ở class tương ứng mà không phải sửa ở hàng trăm file test script.</v>
       </c>
       <c r="F4" t="str">
+        <v>Tự động gửi email thông báo kết quả chạy test cho ban giám đốc hàng giờ — gửi báo cáo hàng giờ</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tách biệt locator và hành vi của từng trang web thành các class độc lập, giúp code test dễ bảo trì và tái sử dụng — thiết kế POM dễ bảo trì</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Tự động vẽ lại sơ đồ cấu trúc cơ sở dữ liệu quan hệ SQL của dự án — vẽ cấu trúc database</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Mã hóa toàn bộ các kịch bản test thành các file ảnh động GIF bảo mật — mã hóa kịch bản test</v>
       </c>
-      <c r="I4" t="str">
-        <v>Tự động gửi email thông báo kết quả chạy test cho ban giám đốc hàng giờ — gửi báo cáo hàng giờ</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Absolute XPath (như `/html/body/div[1]/div[2]/button`) sẽ bị gãy ngay khi cấu trúc trang web thay đổi nhẹ (thêm 1 thẻ div). Relative XPath (như `//button[@id="submit"]`) tìm trực tiếp phần tử có thuộc tính chỉ định, bền bỉ hơn nhiều.</v>
       </c>
       <c r="F5" t="str">
+        <v>Tuyệt đối bắt buộc phải viết bằng ngôn ngữ Java; còn Tương đối viết bằng Python — giới hạn ngôn ngữ lập trình</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tuyệt đối chạy nhanh gấp 10 lần so với đường dẫn tương đối trong mọi trường hợp — so sánh tốc độ</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Tuyệt đối chỉ chạy được trên Google Chrome; còn Tương đối chỉ chạy được trên Safari — giới hạn trình duyệt chạy</v>
+      </c>
+      <c r="I5" t="str">
         <v>Tuyệt đối bắt đầu bằng dấu gạch chéo đơn `/` đi từ gốc html (dễ gãy); Tương đối bắt đầu bằng gạch chéo kép `//` tìm trực tiếp phần tử (ổn định hơn) — bắt đầu từ gốc html vs tìm trực tiếp</v>
       </c>
-      <c r="G5" t="str">
-        <v>Tuyệt đối chỉ chạy được trên Google Chrome; còn Tương đối chỉ chạy được trên Safari — giới hạn trình duyệt chạy</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tuyệt đối bắt buộc phải viết bằng ngôn ngữ Java; còn Tương đối viết bằng Python — giới hạn ngôn ngữ lập trình</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Tuyệt đối chạy nhanh gấp 10 lần so với đường dẫn tương đối trong mọi trường hợp — so sánh tốc độ</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -591,10 +591,10 @@
         <v>Mở trình duyệt -&gt; Nhập username -&gt; Nhập password -&gt; Bấm nút Login -&gt; Kiểm tra xem có hiển thị trang chủ không — luồng đăng nhập tự động</v>
       </c>
       <c r="G6" t="str">
+        <v>Mở trình duyệt -&gt; Thay đổi mật khẩu của admin -&gt; Gửi mã OTP về điện thoại cá nhân — luồng đổi mật khẩu</v>
+      </c>
+      <c r="H6" t="str">
         <v>Mở trình duyệt -&gt; Xóa cơ sở dữ liệu -&gt; Đóng trình duyệt -&gt; Gửi báo cáo lỗi cho khách hàng — luồng xóa dữ liệu lỗi</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Mở trình duyệt -&gt; Thay đổi mật khẩu của admin -&gt; Gửi mã OTP về điện thoại cá nhân — luồng đổi mật khẩu</v>
       </c>
       <c r="I6" t="str">
         <v>Mở trình duyệt -&gt; Vẽ sơ đồ Use Case -&gt; Thiết kế giao diện trang chủ bằng CSS — luồng thiết kế giao diện</v>
@@ -623,13 +623,13 @@
         <v>sendKeys() — dùng để truyền chuỗi ký tự vào phần tử input — gõ text sendKeys</v>
       </c>
       <c r="G7" t="str">
+        <v>getText() — dùng để lấy chuỗi văn bản hiển thị của phần tử ra ngoài — lấy text getText</v>
+      </c>
+      <c r="H7" t="str">
         <v>click() — dùng để bấm chuột vào phần tử nút bấm hoặc liên kết — click chuột click</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>clear() — dùng để xóa sạch dữ liệu text đang có sẵn trong ô nhập — clear text clear</v>
-      </c>
-      <c r="I7" t="str">
-        <v>getText() — dùng để lấy chuỗi văn bản hiển thị của phần tử ra ngoài — lấy text getText</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,10 +652,10 @@
         <v>Assert (Khẳng định) là trái tim của test case. Một script test không có Assert thì chỉ là một bot click chuột tự động, không có khả năng kiểm chứng tính đúng đắn của phần mềm.</v>
       </c>
       <c r="F8" t="str">
+        <v>Tự động chụp ảnh màn hình giao diện khi chạy qua các bước của test script — chụp ảnh màn hình</v>
+      </c>
+      <c r="G8" t="str">
         <v>So sánh kết quả thực tế (Actual) với kết quả mong đợi (Expected) để quyết định test case pass hay fail — so sánh đối chiếu kết quả</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Tự động chụp ảnh màn hình giao diện khi chạy qua các bước của test script — chụp ảnh màn hình</v>
       </c>
       <c r="H8" t="str">
         <v>Mở trình duyệt web ẩn danh để chạy test mà không lưu lại lịch sử — mở trình duyệt ẩn danh</v>
@@ -664,7 +664,7 @@
         <v>Xóa bỏ toàn bộ các biến dữ liệu rác trong bộ nhớ RAM của máy tính chạy test — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -716,19 +716,19 @@
         <v>Implicit Wait cấu hình một lần cho cả phiên chạy (driver lifecycle). Khi tìm kiếm phần tử, nếu chưa thấy, driver sẽ liên tục quét lại (poll) cho đến khi thấy hoặc hết thời gian chờ tối đa.</v>
       </c>
       <c r="F10" t="str">
-        <v>Thiết lập một khoảng thời gian chờ đợi tối đa cho driver tìm kiếm phần tử trước khi ném ra ngoại lệ NoSuchElementException — thời gian chờ ngầm định tìm phần tử</v>
+        <v>Mã hóa toàn bộ mã nguồn của file test script trước khi gửi lên github — mã hóa file test</v>
       </c>
       <c r="G10" t="str">
         <v>Bắt buộc trình duyệt phải dừng hoạt động hoàn toàn trong vòng đúng 10 giây ở mỗi câu lệnh — dừng hoạt động cứng</v>
       </c>
       <c r="H10" t="str">
+        <v>Thiết lập một khoảng thời gian chờ đợi tối đa cho driver tìm kiếm phần tử trước khi ném ra ngoại lệ NoSuchElementException — thời gian chờ ngầm định tìm phần tử</v>
+      </c>
+      <c r="I10" t="str">
         <v>Tự động đóng trình duyệt web ngay khi gặp bất kỳ lỗi logic nào từ code test — tự động đóng trình duyệt</v>
       </c>
-      <c r="I10" t="str">
-        <v>Mã hóa toàn bộ mã nguồn của file test script trước khi gửi lên github — mã hóa file test</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Postman là công cụ phổ biến nhất để kiểm thử API thủ công và tự động hóa các kịch bản kiểm thử API (qua Collection Runner).</v>
       </c>
       <c r="F11" t="str">
+        <v>Performance Testing — chạy giả lập 1,000,000 người dùng truy cập đồng thời để làm sập hệ thống — kiểm thử tải</v>
+      </c>
+      <c r="G11" t="str">
         <v>API Testing — gửi các yêu cầu HTTP (GET, POST...) và kiểm tra kết quả trả về của API — kiểm thử API</v>
-      </c>
-      <c r="G11" t="str">
-        <v>UI Testing — tự động click chuột và kéo thả các phần tử trên trình duyệt web — kiểm thử giao diện đồ họa</v>
       </c>
       <c r="H11" t="str">
         <v>Security Testing — quét lỗ hổng bảo mật và tấn công bẻ khóa mật khẩu hệ thống — kiểm thử bảo mật</v>
       </c>
       <c r="I11" t="str">
-        <v>Performance Testing — chạy giả lập 1,000,000 người dùng truy cập đồng thời để làm sập hệ thống — kiểm thử tải</v>
+        <v>UI Testing — tự động click chuột và kéo thả các phần tử trên trình duyệt web — kiểm thử giao diện đồ họa</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
